--- a/data/raw/Proyectos/centroDeProyectos_PMO_2026.xlsx
+++ b/data/raw/Proyectos/centroDeProyectos_PMO_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Informe_Interactivo/data/proyectos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Proyectos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="11_C027D363B901AF65D94FC13C36333C815A25773C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F7D8C8D-07ED-46AA-B69E-C9E6CC565515}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="11_C027D363B901AF65D94FC13C36333C815A25773C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A176856A-6B8A-4BE7-BC8A-8B7B46131741}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/raw/Proyectos/centroDeProyectos_PMO_2026.xlsx
+++ b/data/raw/Proyectos/centroDeProyectos_PMO_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Proyectos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="11_C027D363B901AF65D94FC13C36333C815A25773C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A176856A-6B8A-4BE7-BC8A-8B7B46131741}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="11_C027D363B901AF65D94FC13C36333C815A25773C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C101444B-2D23-4103-94DA-39C6D92F1046}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2328,7 +2328,7 @@
     <col min="18" max="18" width="23" customWidth="1"/>
     <col min="19" max="19" width="11.109375" customWidth="1"/>
     <col min="21" max="22" width="26.5546875" customWidth="1"/>
-    <col min="23" max="23" width="39.109375" customWidth="1"/>
+    <col min="23" max="23" width="84.5546875" customWidth="1"/>
     <col min="24" max="26" width="55" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/raw/Proyectos/centroDeProyectos_PMO_2026.xlsx
+++ b/data/raw/Proyectos/centroDeProyectos_PMO_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Proyectos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="11_C027D363B901AF65D94FC13C36333C815A25773C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C101444B-2D23-4103-94DA-39C6D92F1046}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="11_C027D363B901AF65D94FC13C36333C815A25773C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCE55333-73E1-4C31-911D-E9BD8FE979DD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="centroDeProyectos" sheetId="1" r:id="rId1"/>
@@ -1957,6 +1957,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A1:Y54" totalsRowShown="0">
+  <autoFilter ref="A1:Y54" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Nombre del proyecto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="0. Estado del proyecto"/>
@@ -2311,25 +2312,29 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.109375" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
-    <col min="5" max="5" width="29.109375" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="10" width="15.44140625" customWidth="1"/>
-    <col min="12" max="12" width="21" customWidth="1"/>
-    <col min="13" max="13" width="21.5546875" customWidth="1"/>
-    <col min="14" max="14" width="30.33203125" customWidth="1"/>
-    <col min="15" max="15" width="22.5546875" customWidth="1"/>
-    <col min="16" max="16" width="31.44140625" customWidth="1"/>
-    <col min="17" max="17" width="23.88671875" customWidth="1"/>
-    <col min="18" max="18" width="23" customWidth="1"/>
-    <col min="19" max="19" width="11.109375" customWidth="1"/>
-    <col min="21" max="22" width="26.5546875" customWidth="1"/>
-    <col min="23" max="23" width="84.5546875" customWidth="1"/>
-    <col min="24" max="26" width="55" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="29.109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="12" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.44140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="21" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="21.5546875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="30.33203125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="22.5546875" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="31.44140625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="23.88671875" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="23" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="11.109375" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
+    <col min="21" max="22" width="26.5546875" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="84.5546875" hidden="1" customWidth="1"/>
+    <col min="24" max="25" width="55" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="55" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
